--- a/docs/lab1/Lab01_ReviewReport.xlsx
+++ b/docs/lab1/Lab01_ReviewReport.xlsx
@@ -1,18 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bogdan\Projects\UBB\vvss-am36\docs\lab1\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEC207B0-AB26-4788-96C8-C5DC59EF4405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="11496" tabRatio="650" activeTab="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" tabRatio="650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Requirements Phase Defects" sheetId="7" r:id="rId1"/>
+    <sheet name="Requirements Phase Defects" sheetId="9" r:id="rId1"/>
     <sheet name="Architect. Design Phase Defects" sheetId="6" r:id="rId2"/>
     <sheet name="Coding Phase Defects" sheetId="5" r:id="rId3"/>
     <sheet name="Tool-basedCodeAnalysis" sheetId="8" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -30,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="74">
   <si>
     <t>Document  Title:</t>
   </si>
@@ -171,19 +177,107 @@
   </si>
   <si>
     <t>Nu exista legatura intre produs si reteta, conform cerintei fiecare reteta apartine unui produs</t>
+  </si>
+  <si>
+    <t>1,5</t>
+  </si>
+  <si>
+    <t>Nu se specifică ce versiune de Java se folosește și pe ce sisteme de operare trebuie să ruleze aplicația</t>
+  </si>
+  <si>
+    <t>pag1 / NF</t>
+  </si>
+  <si>
+    <t>R07</t>
+  </si>
+  <si>
+    <t>Nu este clar utilizatorul țintă</t>
+  </si>
+  <si>
+    <t>pag1</t>
+  </si>
+  <si>
+    <t>R06</t>
+  </si>
+  <si>
+    <t>Nu se specifică ce date ajung în CSV</t>
+  </si>
+  <si>
+    <t>pag1/ CF8</t>
+  </si>
+  <si>
+    <t>R05</t>
+  </si>
+  <si>
+    <t>Nu se specifică ce se întâmplă la prima rulare, atunci când fișierele sunt goale</t>
+  </si>
+  <si>
+    <t>pag1/ NF</t>
+  </si>
+  <si>
+    <t>R04</t>
+  </si>
+  <si>
+    <t>Nu se specifică că produsele ar avea un preț, deci cerința este invalidă</t>
+  </si>
+  <si>
+    <t>pag1 / CF8</t>
+  </si>
+  <si>
+    <t>R03</t>
+  </si>
+  <si>
+    <t>Nu se specifică dacă există diferite tipuri de user</t>
+  </si>
+  <si>
+    <t>R02</t>
+  </si>
+  <si>
+    <t>Nu există cerințe referitoare la validarea datelor</t>
+  </si>
+  <si>
+    <t>Nu se specifică formatul fișierelor CSV</t>
+  </si>
+  <si>
+    <t>pag1 / CF7, CF8</t>
+  </si>
+  <si>
+    <t>R01</t>
+  </si>
+  <si>
+    <t>Nu se specifică nicăieri că produsele ar avea un preț</t>
+  </si>
+  <si>
+    <t>16.03.2026</t>
+  </si>
+  <si>
+    <t>236/1</t>
+  </si>
+  <si>
+    <t>Rezuș Bogdan</t>
+  </si>
+  <si>
+    <t>Răduță Cristian</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="11" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -260,6 +354,14 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -359,89 +461,115 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{D14AA060-1A6D-4540-B182-F5534A8B6575}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -457,9 +585,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -497,7 +625,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -569,7 +697,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -742,262 +870,334 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9CB0876-90F3-45EF-A9BA-DB46A3A08A42}">
   <sheetPr>
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:J27"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="6"/>
-    <col min="2" max="2" width="12.21875" style="6" customWidth="1"/>
-    <col min="3" max="4" width="16.21875" style="6" customWidth="1"/>
-    <col min="5" max="5" width="41.44140625" style="6" customWidth="1"/>
-    <col min="6" max="8" width="8.88671875" style="6"/>
-    <col min="9" max="9" width="21" style="6" customWidth="1"/>
-    <col min="10" max="10" width="14.44140625" style="6" customWidth="1"/>
-    <col min="11" max="16384" width="8.88671875" style="6"/>
+    <col min="1" max="1" width="8.88671875" style="32"/>
+    <col min="2" max="2" width="12.21875" style="32" customWidth="1"/>
+    <col min="3" max="4" width="16.21875" style="32" customWidth="1"/>
+    <col min="5" max="5" width="41.44140625" style="32" customWidth="1"/>
+    <col min="6" max="8" width="8.88671875" style="32"/>
+    <col min="9" max="9" width="21" style="32" customWidth="1"/>
+    <col min="10" max="10" width="14.44140625" style="32" customWidth="1"/>
+    <col min="11" max="16384" width="8.88671875" style="32"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.45" x14ac:dyDescent="0.35">
-      <c r="A1" s="4"/>
-      <c r="B1" s="5" t="s">
+    <row r="1" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="51"/>
+      <c r="B1" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="H1" s="49" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-    </row>
-    <row r="2" spans="1:10" ht="14.55" x14ac:dyDescent="0.35">
-      <c r="B2" s="24" t="s">
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B2" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="19" t="s">
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="J2" s="17" t="s">
+      <c r="J2" s="37" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="14.55" x14ac:dyDescent="0.35">
-      <c r="H3" s="17" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H3" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-    </row>
-    <row r="4" spans="1:10" ht="14.55" x14ac:dyDescent="0.35">
-      <c r="C4" s="13" t="s">
+      <c r="I3" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="J3" s="37" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C4" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="25" t="s">
+      <c r="D4" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="25"/>
-      <c r="H4" s="17" t="s">
+      <c r="E4" s="47"/>
+      <c r="H4" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-    </row>
-    <row r="5" spans="1:10" ht="14.55" x14ac:dyDescent="0.35">
-      <c r="C5" s="13" t="s">
+      <c r="I4" s="37" t="s">
+        <v>72</v>
+      </c>
+      <c r="J4" s="37" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C5" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="26" t="s">
+      <c r="D5" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="27"/>
-      <c r="H5" s="17" t="s">
+      <c r="E5" s="44"/>
+      <c r="H5" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-    </row>
-    <row r="6" spans="1:10" ht="14.55" x14ac:dyDescent="0.35">
-      <c r="B6" s="8"/>
-      <c r="C6" s="9" t="s">
+      <c r="I5" s="37" t="s">
+        <v>33</v>
+      </c>
+      <c r="J5" s="37" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B6" s="43"/>
+      <c r="C6" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-    </row>
-    <row r="7" spans="1:10" ht="14.55" x14ac:dyDescent="0.35">
-      <c r="C7" s="9" t="s">
+      <c r="D6" s="41" t="s">
+        <v>72</v>
+      </c>
+      <c r="E6" s="41"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C7" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
-    </row>
-    <row r="9" spans="1:10" ht="14.55" x14ac:dyDescent="0.35">
-      <c r="B9" s="10" t="s">
+      <c r="D7" s="41" t="s">
+        <v>70</v>
+      </c>
+      <c r="E7" s="41"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B9" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="E9" s="39" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="14.55" x14ac:dyDescent="0.35">
-      <c r="B10" s="3">
+    <row r="10" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B10" s="37">
         <v>1</v>
       </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11" spans="1:10" ht="14.55" x14ac:dyDescent="0.35">
-      <c r="B11" s="3">
+      <c r="C10" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="E10" s="38" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B11" s="37">
         <f>B10+1</f>
         <v>2</v>
       </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12" spans="1:10" ht="14.55" x14ac:dyDescent="0.35">
-      <c r="B12" s="3">
-        <f t="shared" ref="B12:B25" si="0">B11+1</f>
+      <c r="C11" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="D11" s="33" t="s">
+        <v>67</v>
+      </c>
+      <c r="E11" s="38" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B12" s="37">
+        <f>B11+1</f>
         <v>3</v>
       </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="2"/>
-    </row>
-    <row r="13" spans="1:10" ht="14.55" x14ac:dyDescent="0.35">
-      <c r="B13" s="3">
-        <f t="shared" si="0"/>
+      <c r="C12" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="D12" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12" s="38" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B13" s="37">
+        <f>B12+1</f>
         <v>4</v>
       </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="2"/>
-    </row>
-    <row r="14" spans="1:10" ht="14.55" x14ac:dyDescent="0.35">
-      <c r="B14" s="3">
-        <f t="shared" si="0"/>
+      <c r="C13" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="D13" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="E13" s="38" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B14" s="37">
+        <f>B13+1</f>
         <v>5</v>
       </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="2"/>
-    </row>
-    <row r="15" spans="1:10" ht="14.55" x14ac:dyDescent="0.35">
-      <c r="B15" s="3">
-        <f t="shared" si="0"/>
+      <c r="C14" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="D14" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="E14" s="38" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B15" s="37">
+        <f>B14+1</f>
         <v>6</v>
       </c>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="2"/>
-    </row>
-    <row r="16" spans="1:10" ht="14.55" x14ac:dyDescent="0.35">
-      <c r="B16" s="3">
-        <f t="shared" si="0"/>
+      <c r="C15" s="33" t="s">
+        <v>59</v>
+      </c>
+      <c r="D15" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="E15" s="38" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B16" s="37">
+        <f>B15+1</f>
         <v>7</v>
       </c>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="2"/>
-    </row>
-    <row r="17" spans="2:5" ht="14.55" x14ac:dyDescent="0.35">
-      <c r="B17" s="3">
-        <f t="shared" si="0"/>
+      <c r="C16" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="D16" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="E16" s="38" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B17" s="37">
+        <f>B16+1</f>
         <v>8</v>
       </c>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="2"/>
-    </row>
-    <row r="18" spans="2:5" ht="14.55" x14ac:dyDescent="0.35">
-      <c r="B18" s="3">
-        <f t="shared" si="0"/>
+      <c r="C17" s="33" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="E17" s="38" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B18" s="37">
+        <f>B17+1</f>
         <v>9</v>
       </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="15"/>
-    </row>
-    <row r="19" spans="2:5" ht="14.55" x14ac:dyDescent="0.35">
-      <c r="B19" s="3">
-        <f t="shared" si="0"/>
+      <c r="C18" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="E18" s="38" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B19" s="37">
+        <f>B18+1</f>
         <v>10</v>
       </c>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="15"/>
-    </row>
-    <row r="20" spans="2:5" ht="14.55" x14ac:dyDescent="0.35">
-      <c r="B20" s="3">
-        <f t="shared" si="0"/>
+      <c r="C19" s="37"/>
+      <c r="D19" s="37"/>
+      <c r="E19" s="36"/>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="37">
+        <f>B19+1</f>
         <v>11</v>
       </c>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="15"/>
-    </row>
-    <row r="21" spans="2:5" ht="14.55" x14ac:dyDescent="0.35">
-      <c r="B21" s="3">
-        <f t="shared" si="0"/>
+      <c r="C20" s="37"/>
+      <c r="D20" s="37"/>
+      <c r="E20" s="36"/>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B21" s="37">
+        <f>B20+1</f>
         <v>12</v>
       </c>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="15"/>
-    </row>
-    <row r="22" spans="2:5" ht="14.55" x14ac:dyDescent="0.35">
-      <c r="B22" s="3">
-        <f t="shared" si="0"/>
+      <c r="C21" s="37"/>
+      <c r="D21" s="37"/>
+      <c r="E21" s="36"/>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="37">
+        <f>B21+1</f>
         <v>13</v>
       </c>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="15"/>
-    </row>
-    <row r="23" spans="2:5" ht="14.55" x14ac:dyDescent="0.35">
-      <c r="B23" s="3">
-        <f t="shared" si="0"/>
+      <c r="C22" s="37"/>
+      <c r="D22" s="37"/>
+      <c r="E22" s="36"/>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B23" s="37">
+        <f>B22+1</f>
         <v>14</v>
       </c>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="15"/>
-    </row>
-    <row r="24" spans="2:5" ht="14.55" x14ac:dyDescent="0.35">
-      <c r="B24" s="3">
-        <f t="shared" si="0"/>
+      <c r="C23" s="37"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="36"/>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B24" s="37">
+        <f>B23+1</f>
         <v>15</v>
       </c>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="15"/>
-    </row>
-    <row r="25" spans="2:5" ht="14.55" x14ac:dyDescent="0.35">
-      <c r="B25" s="3">
-        <f t="shared" si="0"/>
+      <c r="C24" s="37"/>
+      <c r="D24" s="37"/>
+      <c r="E24" s="36"/>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B25" s="37">
+        <f>B24+1</f>
         <v>16</v>
       </c>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="15"/>
-    </row>
-    <row r="27" spans="2:5" ht="14.55" x14ac:dyDescent="0.35">
-      <c r="C27" s="11" t="s">
+      <c r="C25" s="37"/>
+      <c r="D25" s="37"/>
+      <c r="E25" s="36"/>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C27" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="D27" s="12"/>
-      <c r="E27" s="1"/>
+      <c r="D27" s="34"/>
+      <c r="E27" s="33" t="s">
+        <v>47</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1014,7 +1214,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
@@ -1030,40 +1230,40 @@
     <col min="10" max="16384" width="8.88671875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.45" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="4"/>
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="H1" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-    </row>
-    <row r="2" spans="1:10" ht="14.55" x14ac:dyDescent="0.35">
-      <c r="B2" s="24" t="s">
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B2" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="19" t="s">
+      <c r="I2" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="J2" s="17" t="s">
+      <c r="J2" s="14" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="H3" s="17" t="s">
+      <c r="H3" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="37" t="s">
+      <c r="I3" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="J3" s="17">
+      <c r="J3" s="14">
         <v>236</v>
       </c>
     </row>
@@ -1071,14 +1271,14 @@
       <c r="C4" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="28" t="s">
+      <c r="D4" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="28"/>
-      <c r="H4" s="17" t="s">
+      <c r="E4" s="22"/>
+      <c r="H4" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="37" t="s">
+      <c r="I4" s="19" t="s">
         <v>35</v>
       </c>
       <c r="J4" s="3">
@@ -1089,40 +1289,40 @@
       <c r="C5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="29" t="s">
+      <c r="D5" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="30"/>
-      <c r="H5" s="17" t="s">
+      <c r="E5" s="26"/>
+      <c r="H5" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="37" t="s">
+      <c r="I5" s="19" t="s">
         <v>36</v>
       </c>
       <c r="J5" s="3">
         <v>236</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6" s="8"/>
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="D6" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="22"/>
-    </row>
-    <row r="7" spans="1:10" ht="14.55" x14ac:dyDescent="0.35">
+      <c r="E6" s="23"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="36">
+      <c r="D7" s="24">
         <v>46097</v>
       </c>
-      <c r="E7" s="22"/>
-    </row>
-    <row r="9" spans="1:10" ht="14.55" x14ac:dyDescent="0.35">
+      <c r="E7" s="23"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" s="10" t="s">
         <v>4</v>
       </c>
@@ -1204,7 +1404,7 @@
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:10" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B15" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1213,7 +1413,7 @@
       <c r="D15" s="1"/>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:10" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B16" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1222,7 +1422,7 @@
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
     </row>
-    <row r="17" spans="2:5" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1231,7 +1431,7 @@
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
     </row>
-    <row r="18" spans="2:5" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1240,7 +1440,7 @@
       <c r="D18" s="1"/>
       <c r="E18" s="2"/>
     </row>
-    <row r="19" spans="2:5" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B19" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1249,7 +1449,7 @@
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
     </row>
-    <row r="20" spans="2:5" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -1258,7 +1458,7 @@
       <c r="D20" s="1"/>
       <c r="E20" s="2"/>
     </row>
-    <row r="21" spans="2:5" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B21" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1267,7 +1467,7 @@
       <c r="D21" s="1"/>
       <c r="E21" s="2"/>
     </row>
-    <row r="22" spans="2:5" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -1276,7 +1476,7 @@
       <c r="D22" s="1"/>
       <c r="E22" s="2"/>
     </row>
-    <row r="23" spans="2:5" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B23" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -1285,7 +1485,7 @@
       <c r="D23" s="1"/>
       <c r="E23" s="2"/>
     </row>
-    <row r="24" spans="2:5" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B24" s="3">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -1294,7 +1494,7 @@
       <c r="D24" s="1"/>
       <c r="E24" s="2"/>
     </row>
-    <row r="25" spans="2:5" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B25" s="3">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -1303,7 +1503,7 @@
       <c r="D25" s="1"/>
       <c r="E25" s="2"/>
     </row>
-    <row r="26" spans="2:5" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B26" s="3">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -1312,7 +1512,7 @@
       <c r="D26" s="1"/>
       <c r="E26" s="2"/>
     </row>
-    <row r="28" spans="2:5" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C28" s="11" t="s">
         <v>8</v>
       </c>
@@ -1334,7 +1534,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor theme="3" tint="0.59999389629810485"/>
   </sheetPr>
@@ -1351,83 +1551,83 @@
     <col min="10" max="16384" width="8.88671875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.45" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="4"/>
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="H1" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-    </row>
-    <row r="2" spans="1:10" ht="14.55" x14ac:dyDescent="0.35">
-      <c r="B2" s="24" t="s">
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B2" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="19" t="s">
+      <c r="I2" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="J2" s="17" t="s">
+      <c r="J2" s="14" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="14.55" x14ac:dyDescent="0.35">
-      <c r="H3" s="17" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H3" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-    </row>
-    <row r="4" spans="1:10" ht="14.55" x14ac:dyDescent="0.35">
-      <c r="C4" s="16" t="s">
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C4" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="31" t="s">
+      <c r="D4" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="31"/>
-      <c r="H4" s="17" t="s">
+      <c r="E4" s="27"/>
+      <c r="H4" s="14" t="s">
         <v>21</v>
       </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
     </row>
-    <row r="5" spans="1:10" ht="14.55" x14ac:dyDescent="0.35">
-      <c r="C5" s="16" t="s">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C5" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="32" t="s">
+      <c r="D5" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="33"/>
-      <c r="H5" s="17" t="s">
+      <c r="E5" s="29"/>
+      <c r="H5" s="14" t="s">
         <v>22</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
     </row>
-    <row r="6" spans="1:10" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6" s="8"/>
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-    </row>
-    <row r="7" spans="1:10" ht="14.55" x14ac:dyDescent="0.35">
+      <c r="D6" s="23"/>
+      <c r="E6" s="23"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
-    </row>
-    <row r="9" spans="1:10" ht="14.55" x14ac:dyDescent="0.35">
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" s="10" t="s">
         <v>4</v>
       </c>
@@ -1441,7 +1641,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B10" s="3">
         <v>1</v>
       </c>
@@ -1449,7 +1649,7 @@
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
     </row>
-    <row r="11" spans="1:10" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B11" s="3">
         <f>B10+1</f>
         <v>2</v>
@@ -1458,7 +1658,7 @@
       <c r="D11" s="1"/>
       <c r="E11" s="2"/>
     </row>
-    <row r="12" spans="1:10" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B12" s="3">
         <f t="shared" ref="B12:B30" si="0">B11+1</f>
         <v>3</v>
@@ -1467,7 +1667,7 @@
       <c r="D12" s="1"/>
       <c r="E12" s="2"/>
     </row>
-    <row r="13" spans="1:10" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B13" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1476,7 +1676,7 @@
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" spans="1:10" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B14" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1485,7 +1685,7 @@
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:10" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B15" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1494,7 +1694,7 @@
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:10" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B16" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1503,7 +1703,7 @@
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
     </row>
-    <row r="17" spans="2:5" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1512,7 +1712,7 @@
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
     </row>
-    <row r="18" spans="2:5" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1521,7 +1721,7 @@
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
     </row>
-    <row r="19" spans="2:5" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B19" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1530,7 +1730,7 @@
       <c r="D19" s="1"/>
       <c r="E19" s="2"/>
     </row>
-    <row r="20" spans="2:5" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -1539,7 +1739,7 @@
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
     </row>
-    <row r="21" spans="2:5" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B21" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1548,7 +1748,7 @@
       <c r="D21" s="1"/>
       <c r="E21" s="2"/>
     </row>
-    <row r="22" spans="2:5" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -1557,7 +1757,7 @@
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
     </row>
-    <row r="23" spans="2:5" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B23" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -1566,7 +1766,7 @@
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
     </row>
-    <row r="24" spans="2:5" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B24" s="3">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -1575,7 +1775,7 @@
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
     </row>
-    <row r="25" spans="2:5" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B25" s="3">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -1584,7 +1784,7 @@
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
     </row>
-    <row r="26" spans="2:5" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B26" s="3">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -1593,7 +1793,7 @@
       <c r="D26" s="1"/>
       <c r="E26" s="2"/>
     </row>
-    <row r="27" spans="2:5" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B27" s="3">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -1602,7 +1802,7 @@
       <c r="D27" s="2"/>
       <c r="E27" s="1"/>
     </row>
-    <row r="28" spans="2:5" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B28" s="3">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -1611,7 +1811,7 @@
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
     </row>
-    <row r="29" spans="2:5" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B29" s="3">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -1620,7 +1820,7 @@
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
     </row>
-    <row r="30" spans="2:5" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B30" s="3">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -1629,7 +1829,7 @@
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
     </row>
-    <row r="32" spans="2:5" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C32" s="11" t="s">
         <v>8</v>
       </c>
@@ -1651,7 +1851,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
@@ -1669,73 +1869,73 @@
     <col min="10" max="16384" width="8.88671875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.45" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="4"/>
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="H1" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-    </row>
-    <row r="2" spans="1:10" ht="14.55" x14ac:dyDescent="0.35">
-      <c r="B2" s="24" t="s">
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B2" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="19" t="s">
+      <c r="I2" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="J2" s="17" t="s">
+      <c r="J2" s="14" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="14.55" x14ac:dyDescent="0.35">
-      <c r="H3" s="17" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H3" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-    </row>
-    <row r="4" spans="1:10" ht="14.55" x14ac:dyDescent="0.35">
-      <c r="C4" s="16" t="s">
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C4" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
-      <c r="H4" s="17" t="s">
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="H4" s="14" t="s">
         <v>21</v>
       </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
     </row>
-    <row r="5" spans="1:10" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C5" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="H5" s="17" t="s">
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="H5" s="14" t="s">
         <v>22</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
     </row>
-    <row r="6" spans="1:10" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6" s="8"/>
       <c r="C6" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="20"/>
-    </row>
-    <row r="9" spans="1:10" ht="14.55" x14ac:dyDescent="0.35">
+      <c r="D6" s="23"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="17"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" s="10" t="s">
         <v>4</v>
       </c>
@@ -1752,7 +1952,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B10" s="3">
         <v>1</v>
       </c>
@@ -1761,7 +1961,7 @@
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
     </row>
-    <row r="11" spans="1:10" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B11" s="3">
         <f>B10+1</f>
         <v>2</v>
@@ -1771,7 +1971,7 @@
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
     </row>
-    <row r="12" spans="1:10" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B12" s="3">
         <f t="shared" ref="B12:B30" si="0">B11+1</f>
         <v>3</v>
@@ -1781,7 +1981,7 @@
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
     </row>
-    <row r="13" spans="1:10" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B13" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1791,7 +1991,7 @@
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
     </row>
-    <row r="14" spans="1:10" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B14" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1801,7 +2001,7 @@
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
     </row>
-    <row r="15" spans="1:10" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B15" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1811,7 +2011,7 @@
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
     </row>
-    <row r="16" spans="1:10" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B16" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1821,7 +2021,7 @@
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
     </row>
-    <row r="17" spans="2:6" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B17" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1831,7 +2031,7 @@
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
     </row>
-    <row r="18" spans="2:6" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B18" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1841,7 +2041,7 @@
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
     </row>
-    <row r="19" spans="2:6" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B19" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1851,7 +2051,7 @@
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
     </row>
-    <row r="20" spans="2:6" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B20" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -1861,7 +2061,7 @@
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
     </row>
-    <row r="21" spans="2:6" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B21" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1871,7 +2071,7 @@
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
     </row>
-    <row r="22" spans="2:6" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B22" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -1881,7 +2081,7 @@
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
     </row>
-    <row r="23" spans="2:6" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B23" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -1891,7 +2091,7 @@
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
     </row>
-    <row r="24" spans="2:6" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B24" s="3">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -1901,7 +2101,7 @@
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
     </row>
-    <row r="25" spans="2:6" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B25" s="3">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -1911,7 +2111,7 @@
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
     </row>
-    <row r="26" spans="2:6" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B26" s="3">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -1921,7 +2121,7 @@
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
     </row>
-    <row r="27" spans="2:6" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B27" s="3">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -1931,7 +2131,7 @@
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
     </row>
-    <row r="28" spans="2:6" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B28" s="3">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -1941,7 +2141,7 @@
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
     </row>
-    <row r="29" spans="2:6" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B29" s="3">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -1951,7 +2151,7 @@
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
     </row>
-    <row r="30" spans="2:6" ht="14.55" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B30" s="3">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -1961,16 +2161,16 @@
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
     </row>
-    <row r="32" spans="2:6" ht="14.55" x14ac:dyDescent="0.35">
-      <c r="C32" s="34" t="s">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="C32" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="D32" s="35"/>
-      <c r="E32" s="35"/>
-      <c r="F32" s="18"/>
-    </row>
-    <row r="35" spans="6:6" ht="14.55" x14ac:dyDescent="0.35">
-      <c r="F35" s="21"/>
+      <c r="D32" s="31"/>
+      <c r="E32" s="31"/>
+      <c r="F32" s="15"/>
+    </row>
+    <row r="35" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="F35" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/docs/lab1/Lab01_ReviewReport.xlsx
+++ b/docs/lab1/Lab01_ReviewReport.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bogdan\Projects\UBB\vvss-am36\docs\lab1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Personal\Programming\Java\VVSS\vvss-am36\docs\lab1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEC207B0-AB26-4788-96C8-C5DC59EF4405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF49EF18-8AC0-4CAC-B6D3-4B3C7F8664FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" tabRatio="650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28695" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="650" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements Phase Defects" sheetId="9" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="83">
   <si>
     <t>Document  Title:</t>
   </si>
@@ -258,19 +258,53 @@
   </si>
   <si>
     <t>Răduță Cristian</t>
+  </si>
+  <si>
+    <t>C01</t>
+  </si>
+  <si>
+    <t>C02</t>
+  </si>
+  <si>
+    <t>OrderValidator / 29</t>
+  </si>
+  <si>
+    <t>Nu se verifica daca total price e 0, doar daca e negativ</t>
+  </si>
+  <si>
+    <t>CsvExporter/22</t>
+  </si>
+  <si>
+    <t>Se foloseste totalul din OrderItem, care poate sa fie incorect daca se modifica intre timp produsul</t>
+  </si>
+  <si>
+    <t>C11</t>
+  </si>
+  <si>
+    <t>Majoritatea Service-urilor</t>
+  </si>
+  <si>
+    <t>Se prescurteaza numele de parametrii la prima litera, nu e destul de clar si nu e consistent</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -463,109 +497,110 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -877,325 +912,325 @@
   <dimension ref="A1:J27"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="32"/>
-    <col min="2" max="2" width="12.21875" style="32" customWidth="1"/>
-    <col min="3" max="4" width="16.21875" style="32" customWidth="1"/>
-    <col min="5" max="5" width="41.44140625" style="32" customWidth="1"/>
-    <col min="6" max="8" width="8.88671875" style="32"/>
-    <col min="9" max="9" width="21" style="32" customWidth="1"/>
-    <col min="10" max="10" width="14.44140625" style="32" customWidth="1"/>
-    <col min="11" max="16384" width="8.88671875" style="32"/>
+    <col min="1" max="1" width="8.88671875" style="20"/>
+    <col min="2" max="2" width="12.21875" style="20" customWidth="1"/>
+    <col min="3" max="4" width="16.21875" style="20" customWidth="1"/>
+    <col min="5" max="5" width="41.44140625" style="20" customWidth="1"/>
+    <col min="6" max="8" width="8.88671875" style="20"/>
+    <col min="9" max="9" width="21" style="20" customWidth="1"/>
+    <col min="10" max="10" width="14.44140625" style="20" customWidth="1"/>
+    <col min="11" max="16384" width="8.88671875" style="20"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="51"/>
-      <c r="B1" s="50" t="s">
+      <c r="A1" s="33"/>
+      <c r="B1" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="49" t="s">
+      <c r="H1" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="48" t="s">
+      <c r="B2" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37" t="s">
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="J2" s="37" t="s">
+      <c r="J2" s="25" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="H3" s="37" t="s">
+      <c r="H3" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="37" t="s">
+      <c r="I3" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="J3" s="37" t="s">
+      <c r="J3" s="25" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C4" s="46" t="s">
+      <c r="C4" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="47" t="s">
+      <c r="D4" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="47"/>
-      <c r="H4" s="37" t="s">
+      <c r="E4" s="37"/>
+      <c r="H4" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="37" t="s">
+      <c r="I4" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="J4" s="37" t="s">
+      <c r="J4" s="25" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C5" s="46" t="s">
+      <c r="C5" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="45" t="s">
+      <c r="D5" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="44"/>
-      <c r="H5" s="37" t="s">
+      <c r="E5" s="39"/>
+      <c r="H5" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="37" t="s">
+      <c r="I5" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="J5" s="37" t="s">
+      <c r="J5" s="25" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B6" s="43"/>
-      <c r="C6" s="42" t="s">
+      <c r="B6" s="30"/>
+      <c r="C6" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="41" t="s">
+      <c r="D6" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="E6" s="41"/>
+      <c r="E6" s="34"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C7" s="42" t="s">
+      <c r="C7" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="41" t="s">
+      <c r="D7" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="E7" s="41"/>
+      <c r="E7" s="34"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B9" s="40" t="s">
+      <c r="B9" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="40" t="s">
+      <c r="C9" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="40" t="s">
+      <c r="D9" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="E9" s="39" t="s">
+      <c r="E9" s="27" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B10" s="37">
+      <c r="B10" s="25">
         <v>1</v>
       </c>
-      <c r="C10" s="33" t="s">
+      <c r="C10" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="D10" s="33" t="s">
+      <c r="D10" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="E10" s="38" t="s">
+      <c r="E10" s="26" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B11" s="37">
-        <f>B10+1</f>
+      <c r="B11" s="25">
+        <f t="shared" ref="B11:B25" si="0">B10+1</f>
         <v>2</v>
       </c>
-      <c r="C11" s="33" t="s">
+      <c r="C11" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="D11" s="33" t="s">
+      <c r="D11" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="E11" s="38" t="s">
+      <c r="E11" s="26" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B12" s="37">
-        <f>B11+1</f>
+      <c r="B12" s="25">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C12" s="33" t="s">
+      <c r="C12" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="D12" s="33" t="s">
+      <c r="D12" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="E12" s="38" t="s">
+      <c r="E12" s="26" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B13" s="37">
-        <f>B12+1</f>
+      <c r="B13" s="25">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="33" t="s">
+      <c r="C13" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="D13" s="33" t="s">
+      <c r="D13" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="E13" s="38" t="s">
+      <c r="E13" s="26" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B14" s="37">
-        <f>B13+1</f>
+      <c r="B14" s="25">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="33" t="s">
+      <c r="C14" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="D14" s="33" t="s">
+      <c r="D14" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="E14" s="38" t="s">
+      <c r="E14" s="26" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B15" s="37">
-        <f>B14+1</f>
+      <c r="B15" s="25">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="33" t="s">
+      <c r="C15" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="D15" s="33" t="s">
+      <c r="D15" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="E15" s="38" t="s">
+      <c r="E15" s="26" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B16" s="37">
-        <f>B15+1</f>
+      <c r="B16" s="25">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="33" t="s">
+      <c r="C16" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="D16" s="33" t="s">
+      <c r="D16" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="E16" s="38" t="s">
+      <c r="E16" s="26" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B17" s="37">
-        <f>B16+1</f>
+      <c r="B17" s="25">
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="33" t="s">
+      <c r="C17" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="D17" s="33" t="s">
+      <c r="D17" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="E17" s="38" t="s">
+      <c r="E17" s="26" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="18" spans="2:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B18" s="37">
-        <f>B17+1</f>
+      <c r="B18" s="25">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="33" t="s">
+      <c r="C18" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="D18" s="33" t="s">
+      <c r="D18" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="E18" s="38" t="s">
+      <c r="E18" s="26" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B19" s="37">
-        <f>B18+1</f>
+      <c r="B19" s="25">
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="37"/>
-      <c r="D19" s="37"/>
-      <c r="E19" s="36"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="24"/>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="37">
-        <f>B19+1</f>
+      <c r="B20" s="25">
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="37"/>
-      <c r="D20" s="37"/>
-      <c r="E20" s="36"/>
+      <c r="C20" s="25"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="24"/>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B21" s="37">
-        <f>B20+1</f>
+      <c r="B21" s="25">
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="37"/>
-      <c r="D21" s="37"/>
-      <c r="E21" s="36"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="24"/>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="37">
-        <f>B21+1</f>
+      <c r="B22" s="25">
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="37"/>
-      <c r="D22" s="37"/>
-      <c r="E22" s="36"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="24"/>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B23" s="37">
-        <f>B22+1</f>
+      <c r="B23" s="25">
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="37"/>
-      <c r="D23" s="37"/>
-      <c r="E23" s="36"/>
+      <c r="C23" s="25"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="24"/>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B24" s="37">
-        <f>B23+1</f>
+      <c r="B24" s="25">
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C24" s="37"/>
-      <c r="D24" s="37"/>
-      <c r="E24" s="36"/>
+      <c r="C24" s="25"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="24"/>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B25" s="37">
-        <f>B24+1</f>
+      <c r="B25" s="25">
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="37"/>
-      <c r="D25" s="37"/>
-      <c r="E25" s="36"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="24"/>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="C27" s="35" t="s">
+      <c r="C27" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D27" s="34"/>
-      <c r="E27" s="33" t="s">
+      <c r="D27" s="22"/>
+      <c r="E27" s="21" t="s">
         <v>47</v>
       </c>
     </row>
@@ -1235,19 +1270,19 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="20" t="s">
+      <c r="H1" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
       <c r="H2" s="3"/>
       <c r="I2" s="16" t="s">
         <v>30</v>
@@ -1271,10 +1306,10 @@
       <c r="C4" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="22" t="s">
+      <c r="D4" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="22"/>
+      <c r="E4" s="42"/>
       <c r="H4" s="14" t="s">
         <v>21</v>
       </c>
@@ -1289,10 +1324,10 @@
       <c r="C5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="25" t="s">
+      <c r="D5" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="26"/>
+      <c r="E5" s="46"/>
       <c r="H5" s="14" t="s">
         <v>22</v>
       </c>
@@ -1308,19 +1343,19 @@
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="D6" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="23"/>
+      <c r="E6" s="43"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="44">
         <v>46097</v>
       </c>
-      <c r="E7" s="23"/>
+      <c r="E7" s="43"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" s="10" t="s">
@@ -1544,7 +1579,7 @@
     <col min="1" max="1" width="8.88671875" style="6"/>
     <col min="2" max="2" width="12.21875" style="6" customWidth="1"/>
     <col min="3" max="3" width="16.21875" style="6" customWidth="1"/>
-    <col min="4" max="4" width="18" style="6" customWidth="1"/>
+    <col min="4" max="4" width="21.88671875" style="6" customWidth="1"/>
     <col min="5" max="5" width="41.44140625" style="6" customWidth="1"/>
     <col min="6" max="8" width="8.88671875" style="6"/>
     <col min="9" max="9" width="26.77734375" style="6" customWidth="1"/>
@@ -1556,19 +1591,19 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="20" t="s">
+      <c r="H1" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
       <c r="H2" s="3"/>
       <c r="I2" s="16" t="s">
         <v>30</v>
@@ -1588,10 +1623,10 @@
       <c r="C4" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="27" t="s">
+      <c r="D4" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="27"/>
+      <c r="E4" s="47"/>
       <c r="H4" s="14" t="s">
         <v>21</v>
       </c>
@@ -1602,10 +1637,10 @@
       <c r="C5" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="28" t="s">
+      <c r="D5" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="29"/>
+      <c r="E5" s="49"/>
       <c r="H5" s="14" t="s">
         <v>22</v>
       </c>
@@ -1617,15 +1652,15 @@
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
+      <c r="D6" s="43"/>
+      <c r="E6" s="43"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="23"/>
-      <c r="E7" s="23"/>
+      <c r="D7" s="43"/>
+      <c r="E7" s="43"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" s="10" t="s">
@@ -1641,31 +1676,49 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B10" s="3">
         <v>1</v>
       </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
+      <c r="C10" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B11" s="3">
         <f>B10+1</f>
         <v>2</v>
       </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C11" s="52" t="s">
+        <v>74</v>
+      </c>
+      <c r="D11" s="52" t="s">
+        <v>78</v>
+      </c>
+      <c r="E11" s="52" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B12" s="3">
         <f t="shared" ref="B12:B30" si="0">B11+1</f>
         <v>3</v>
       </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="2"/>
+      <c r="C12" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B13" s="3">
@@ -1874,19 +1927,19 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="20" t="s">
+      <c r="H1" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
       <c r="H2" s="3"/>
       <c r="I2" s="16" t="s">
         <v>30</v>
@@ -1906,8 +1959,8 @@
       <c r="C4" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="47"/>
       <c r="H4" s="14" t="s">
         <v>21</v>
       </c>
@@ -1918,8 +1971,8 @@
       <c r="C5" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="23"/>
-      <c r="E5" s="23"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
       <c r="H5" s="14" t="s">
         <v>22</v>
       </c>
@@ -1931,8 +1984,8 @@
       <c r="C6" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
+      <c r="D6" s="43"/>
+      <c r="E6" s="43"/>
       <c r="F6" s="17"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
@@ -2162,11 +2215,11 @@
       <c r="F30" s="2"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="C32" s="30" t="s">
+      <c r="C32" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="D32" s="31"/>
-      <c r="E32" s="31"/>
+      <c r="D32" s="51"/>
+      <c r="E32" s="51"/>
       <c r="F32" s="15"/>
     </row>
     <row r="35" spans="6:6" x14ac:dyDescent="0.3">

--- a/docs/lab1/Lab01_ReviewReport.xlsx
+++ b/docs/lab1/Lab01_ReviewReport.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Personal\Programming\Java\VVSS\vvss-am36\docs\lab1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF49EF18-8AC0-4CAC-B6D3-4B3C7F8664FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEDFEC22-BD3C-4B74-BAAF-6331E0B93FD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="650" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="625" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements Phase Defects" sheetId="9" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="109">
   <si>
     <t>Document  Title:</t>
   </si>
@@ -285,6 +285,84 @@
   </si>
   <si>
     <t>Se prescurteaza numele de parametrii la prima litera, nu e destul de clar si nu e consistent</t>
+  </si>
+  <si>
+    <t>ProductValidator / 21</t>
+  </si>
+  <si>
+    <t>ProductValidator / 18</t>
+  </si>
+  <si>
+    <t>Nu se verifica daca cantitatea e 0, doar daca e negativa</t>
+  </si>
+  <si>
+    <t>Nu se verifica daca stocul e 0, doar daca e negativ</t>
+  </si>
+  <si>
+    <t>DrinkShopController + UI</t>
+  </si>
+  <si>
+    <t>Nu este implementata interfata pentru a gestiona stocul</t>
+  </si>
+  <si>
+    <t>Nu se consuma stocul</t>
+  </si>
+  <si>
+    <t>Cantitatea si minimul sunt double in loc de integer</t>
+  </si>
+  <si>
+    <t>DrinkShopService / 65</t>
+  </si>
+  <si>
+    <t>C21</t>
+  </si>
+  <si>
+    <t>Stoc / 7, 8</t>
+  </si>
+  <si>
+    <t>AbstractRepository, 21 21</t>
+  </si>
+  <si>
+    <t>Sections of code should not be commented out</t>
+  </si>
+  <si>
+    <t>SonarQube</t>
+  </si>
+  <si>
+    <t>Define a constant instead of duplicating this literal "Introduceți un nume." 4 times.SonarQube: Duplication</t>
+  </si>
+  <si>
+    <t>SonarQube: Make non-static "product" transient or serializable</t>
+  </si>
+  <si>
+    <t>DrinkShopController, 306</t>
+  </si>
+  <si>
+    <t>OrderItem, 7</t>
+  </si>
+  <si>
+    <t>ProductService, 59</t>
+  </si>
+  <si>
+    <t>SonarQube: Change the visibility of this constructor to "protected".</t>
+  </si>
+  <si>
+    <t>Replace this usage of 'Stream.collect(Collectors.toList())' with 'Stream.toList()' and ensure that the list is unmodified.</t>
+  </si>
+  <si>
+    <t>FileAbstractRepository, 12</t>
+  </si>
+  <si>
+    <t>Rename this generic name to match the regulare expression ''^[A-Z][0-9]?$"</t>
+  </si>
+  <si>
+    <t>FileAbstractRepository, 7</t>
+  </si>
+  <si>
+    <t>Use "isEmpty()" to check whether a "StringBuilder" is empty or not.</t>
+  </si>
+  <si>
+    <t>FileOrderRepository</t>
   </si>
 </sst>
 </file>
@@ -499,7 +577,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -600,7 +678,10 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -617,6 +698,627 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>3714750</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>4097198</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>396240</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F2CB3268-4BCF-2CA0-20B1-0EE0B4C57A8E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6962775" y="1724025"/>
+          <a:ext cx="4102913" cy="323850"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>62865</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>7406</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>77269</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>419196</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{90BAF4C0-4962-0BE7-2A82-C46BB9804F20}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11169015" y="1655231"/>
+          <a:ext cx="4519729" cy="411790"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>3145563</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>379131</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BA1BCB31-BF8F-EAB6-8BEF-1877B0923790}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7200900" y="2209800"/>
+          <a:ext cx="2922678" cy="255306"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>265449</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>453441</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FB56DD5E-1F79-E8C0-F749-370EB41623E7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11191875" y="2181225"/>
+          <a:ext cx="4685049" cy="358191"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>621030</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>72390</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1371705</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>400095</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7785A426-4D10-7BF3-AD75-9C7E76ECB66E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7593330" y="2710815"/>
+          <a:ext cx="750675" cy="327705"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>53340</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>529590</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>457716</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>78181</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3377D2A5-A029-FD27-6EC1-111CD61F158A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11159490" y="2615565"/>
+          <a:ext cx="3690501" cy="539191"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2949349</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>552524</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Picture 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E68850CB-34C5-43FB-C9BE-0C06CE623038}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6987540" y="3076575"/>
+          <a:ext cx="2926489" cy="539189"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>9783</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>415290</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>516339</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Picture 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C667FAA1-917F-AF9D-DC94-0804464EE68A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11201400" y="3086358"/>
+          <a:ext cx="4215765" cy="510366"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>521971</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>3145155</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>95149</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="Picture 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5DF2F67C-4CB3-D8F5-392E-C5AC7B387D45}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7010400" y="3598546"/>
+          <a:ext cx="3114675" cy="710463"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>4095750</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>559013</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>3025140</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>59167</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="Picture 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E70640C-FE00-87DA-D64C-E7E4B749D5AB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11068050" y="3635588"/>
+          <a:ext cx="3059430" cy="631724"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>386715</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>221828</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>969726</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>511428</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="Picture 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7F33A60-655F-4EAC-5671-D7301613A642}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7359015" y="4422353"/>
+          <a:ext cx="586821" cy="293410"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>379095</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>141818</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>874464</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>513346</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="Picture 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31D899C3-A817-2F35-F1A6-1F48FCBA2B09}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11485245" y="4342343"/>
+          <a:ext cx="495369" cy="379148"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>333375</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2189104</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>653503</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="17" name="Picture 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD0E22B7-1C04-7930-1A20-592B7E14D84D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7305675" y="4867275"/>
+          <a:ext cx="1855729" cy="624928"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>4112895</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>64770</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1678542</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>663024</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="Picture 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{193B6BFE-30D4-40CE-44F0-195B68A719AD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11085195" y="4903470"/>
+          <a:ext cx="1699497" cy="598254"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1616,8 +2318,12 @@
       <c r="H3" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
+      <c r="I3" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="J3" s="14">
+        <v>236</v>
+      </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C4" s="13" t="s">
@@ -1630,8 +2336,12 @@
       <c r="H4" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
+      <c r="I4" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="J4" s="3">
+        <v>236</v>
+      </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C5" s="13" t="s">
@@ -1644,22 +2354,30 @@
       <c r="H5" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
+      <c r="I5" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="J5" s="3">
+        <v>236</v>
+      </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6" s="8"/>
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="43"/>
+      <c r="D6" s="43" t="s">
+        <v>73</v>
+      </c>
       <c r="E6" s="43"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="43"/>
+      <c r="D7" s="44">
+        <v>46097</v>
+      </c>
       <c r="E7" s="43"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
@@ -1690,7 +2408,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B11" s="3">
         <f>B10+1</f>
         <v>2</v>
@@ -1701,7 +2419,7 @@
       <c r="D11" s="52" t="s">
         <v>78</v>
       </c>
-      <c r="E11" s="52" t="s">
+      <c r="E11" s="53" t="s">
         <v>79</v>
       </c>
     </row>
@@ -1720,50 +2438,80 @@
         <v>82</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B13" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C13" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B14" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C14" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B15" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="1"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
+      <c r="C15" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B16" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="1"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C16" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B17" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="1"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
+      <c r="C17" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18" s="3">
@@ -1772,7 +2520,7 @@
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
+      <c r="E18" s="3"/>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B19" s="3">
@@ -1887,7 +2635,9 @@
         <v>8</v>
       </c>
       <c r="D32" s="12"/>
-      <c r="E32" s="1"/>
+      <c r="E32" s="1">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1913,10 +2663,10 @@
   <cols>
     <col min="1" max="1" width="8.88671875" style="6"/>
     <col min="2" max="2" width="12.21875" style="6" customWidth="1"/>
-    <col min="3" max="3" width="16.21875" style="6" customWidth="1"/>
-    <col min="4" max="4" width="18" style="6" customWidth="1"/>
-    <col min="5" max="5" width="23.88671875" style="6" customWidth="1"/>
-    <col min="6" max="6" width="16.6640625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="26.21875" style="6" customWidth="1"/>
+    <col min="4" max="4" width="54.33203125" style="6" customWidth="1"/>
+    <col min="5" max="5" width="60.33203125" style="6" customWidth="1"/>
+    <col min="6" max="6" width="47.88671875" style="6" customWidth="1"/>
     <col min="7" max="8" width="8.88671875" style="6"/>
     <col min="9" max="9" width="26.77734375" style="6" customWidth="1"/>
     <col min="10" max="16384" width="8.88671875" style="6"/>
@@ -1952,39 +2702,57 @@
       <c r="H3" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
+      <c r="I3" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="J3" s="14">
+        <v>236</v>
+      </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C4" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="47"/>
+      <c r="D4" s="47" t="s">
+        <v>96</v>
+      </c>
       <c r="E4" s="47"/>
       <c r="H4" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
+      <c r="I4" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="J4" s="3">
+        <v>236</v>
+      </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C5" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="43"/>
+      <c r="D5" s="43" t="s">
+        <v>73</v>
+      </c>
       <c r="E5" s="43"/>
       <c r="H5" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
+      <c r="I5" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="J5" s="3">
+        <v>236</v>
+      </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6" s="8"/>
       <c r="C6" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="43"/>
+      <c r="D6" s="44">
+        <v>46097</v>
+      </c>
       <c r="E6" s="43"/>
       <c r="F6" s="17"/>
     </row>
@@ -2005,72 +2773,100 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="3">
         <v>1</v>
       </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="2"/>
+      <c r="C10" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>95</v>
+      </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="43.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="3">
         <f>B10+1</f>
         <v>2</v>
       </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
+      <c r="C11" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="3">
         <f t="shared" ref="B12:B30" si="0">B11+1</f>
         <v>3</v>
       </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
+      <c r="C12" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>98</v>
+      </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="2"/>
+      <c r="C13" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>103</v>
+      </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="2"/>
+      <c r="C14" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>102</v>
+      </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="1"/>
-      <c r="D15" s="2"/>
+      <c r="C15" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>105</v>
+      </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" ht="56.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="1"/>
-      <c r="D16" s="2"/>
+      <c r="C16" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>107</v>
+      </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
     </row>
@@ -2236,5 +3032,6 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/docs/lab1/Lab01_ReviewReport.xlsx
+++ b/docs/lab1/Lab01_ReviewReport.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Personal\Programming\Java\VVSS\vvss-am36\docs\lab1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEDFEC22-BD3C-4B74-BAAF-6331E0B93FD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF4DD41B-EE54-4C4C-8216-F57D8C4C0737}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="625" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="110">
   <si>
     <t>Document  Title:</t>
   </si>
@@ -363,19 +363,29 @@
   </si>
   <si>
     <t>FileOrderRepository</t>
+  </si>
+  <si>
+    <t>2 clase complet analizate si corectate</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -575,113 +585,114 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1241,7 +1252,7 @@
       <xdr:col>4</xdr:col>
       <xdr:colOff>2189104</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>653503</xdr:rowOff>
+      <xdr:rowOff>657313</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1310,6 +1321,50 @@
         <a:xfrm>
           <a:off x="11085195" y="4903470"/>
           <a:ext cx="1699497" cy="598254"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>3533775</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>91896</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C7BDB343-331F-328D-BF26-98F300050E07}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1447800" y="9172576"/>
+          <a:ext cx="5334000" cy="996770"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1629,19 +1684,19 @@
       <c r="B1" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="35" t="s">
+      <c r="H1" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="44"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
       <c r="H2" s="25"/>
       <c r="I2" s="25" t="s">
         <v>30</v>
@@ -1665,10 +1720,10 @@
       <c r="C4" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="37" t="s">
+      <c r="D4" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="37"/>
+      <c r="E4" s="46"/>
       <c r="H4" s="25" t="s">
         <v>21</v>
       </c>
@@ -1683,10 +1738,10 @@
       <c r="C5" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="38" t="s">
+      <c r="D5" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="39"/>
+      <c r="E5" s="48"/>
       <c r="H5" s="25" t="s">
         <v>22</v>
       </c>
@@ -1702,19 +1757,19 @@
       <c r="C6" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="34" t="s">
+      <c r="D6" s="43" t="s">
         <v>72</v>
       </c>
-      <c r="E6" s="34"/>
+      <c r="E6" s="43"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C7" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="34" t="s">
+      <c r="D7" s="43" t="s">
         <v>70</v>
       </c>
-      <c r="E7" s="34"/>
+      <c r="E7" s="43"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" s="28" t="s">
@@ -1972,19 +2027,19 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="40" t="s">
+      <c r="H1" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
       <c r="H2" s="3"/>
       <c r="I2" s="16" t="s">
         <v>30</v>
@@ -2008,10 +2063,10 @@
       <c r="C4" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="42" t="s">
+      <c r="D4" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="42"/>
+      <c r="E4" s="49"/>
       <c r="H4" s="14" t="s">
         <v>21</v>
       </c>
@@ -2026,10 +2081,10 @@
       <c r="C5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="45" t="s">
+      <c r="D5" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="46"/>
+      <c r="E5" s="51"/>
       <c r="H5" s="14" t="s">
         <v>22</v>
       </c>
@@ -2045,19 +2100,19 @@
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="43" t="s">
+      <c r="D6" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="43"/>
+      <c r="E6" s="41"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="44">
+      <c r="D7" s="42">
         <v>46097</v>
       </c>
-      <c r="E7" s="43"/>
+      <c r="E7" s="41"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" s="10" t="s">
@@ -2293,19 +2348,19 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="40" t="s">
+      <c r="H1" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
       <c r="H2" s="3"/>
       <c r="I2" s="16" t="s">
         <v>30</v>
@@ -2329,10 +2384,10 @@
       <c r="C4" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="47" t="s">
+      <c r="D4" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="47"/>
+      <c r="E4" s="40"/>
       <c r="H4" s="14" t="s">
         <v>21</v>
       </c>
@@ -2347,10 +2402,10 @@
       <c r="C5" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="48" t="s">
+      <c r="D5" s="52" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="49"/>
+      <c r="E5" s="53"/>
       <c r="H5" s="14" t="s">
         <v>22</v>
       </c>
@@ -2366,19 +2421,19 @@
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="43" t="s">
+      <c r="D6" s="41" t="s">
         <v>73</v>
       </c>
-      <c r="E6" s="43"/>
+      <c r="E6" s="41"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="44">
+      <c r="D7" s="42">
         <v>46097</v>
       </c>
-      <c r="E7" s="43"/>
+      <c r="E7" s="41"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" s="10" t="s">
@@ -2413,13 +2468,13 @@
         <f>B10+1</f>
         <v>2</v>
       </c>
-      <c r="C11" s="52" t="s">
+      <c r="C11" s="34" t="s">
         <v>74</v>
       </c>
-      <c r="D11" s="52" t="s">
+      <c r="D11" s="34" t="s">
         <v>78</v>
       </c>
-      <c r="E11" s="53" t="s">
+      <c r="E11" s="35" t="s">
         <v>79</v>
       </c>
     </row>
@@ -2658,7 +2713,7 @@
   <sheetPr>
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="6"/>
@@ -2677,19 +2732,19 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="40" t="s">
+      <c r="H1" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
       <c r="H2" s="3"/>
       <c r="I2" s="16" t="s">
         <v>30</v>
@@ -2713,10 +2768,10 @@
       <c r="C4" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="47" t="s">
+      <c r="D4" s="40" t="s">
         <v>96</v>
       </c>
-      <c r="E4" s="47"/>
+      <c r="E4" s="40"/>
       <c r="H4" s="14" t="s">
         <v>21</v>
       </c>
@@ -2731,10 +2786,10 @@
       <c r="C5" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="43" t="s">
+      <c r="D5" s="41" t="s">
         <v>73</v>
       </c>
-      <c r="E5" s="43"/>
+      <c r="E5" s="41"/>
       <c r="H5" s="14" t="s">
         <v>22</v>
       </c>
@@ -2750,10 +2805,10 @@
       <c r="C6" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="44">
+      <c r="D6" s="42">
         <v>46097</v>
       </c>
-      <c r="E6" s="43"/>
+      <c r="E6" s="41"/>
       <c r="F6" s="17"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
@@ -3011,15 +3066,22 @@
       <c r="F30" s="2"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="C32" s="50" t="s">
+      <c r="C32" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="D32" s="51"/>
-      <c r="E32" s="51"/>
-      <c r="F32" s="15"/>
-    </row>
-    <row r="35" spans="6:6" x14ac:dyDescent="0.3">
+      <c r="D32" s="37"/>
+      <c r="E32" s="37"/>
+      <c r="F32" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="3:6" x14ac:dyDescent="0.3">
       <c r="F35" s="18"/>
+    </row>
+    <row r="36" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C36" s="54" t="s">
+        <v>109</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/docs/lab1/Lab01_ReviewReport.xlsx
+++ b/docs/lab1/Lab01_ReviewReport.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Personal\Programming\Java\VVSS\vvss-am36\docs\lab1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF4DD41B-EE54-4C4C-8216-F57D8C4C0737}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB2BB67E-310C-4E0E-8324-51F0F4D8EFCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="625" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="625" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements Phase Defects" sheetId="9" r:id="rId1"/>
@@ -638,6 +638,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -692,7 +693,6 @@
     <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1684,19 +1684,19 @@
       <c r="B1" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="44" t="s">
+      <c r="H1" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="45"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
       <c r="H2" s="25"/>
       <c r="I2" s="25" t="s">
         <v>30</v>
@@ -1720,10 +1720,10 @@
       <c r="C4" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="46" t="s">
+      <c r="D4" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="46"/>
+      <c r="E4" s="47"/>
       <c r="H4" s="25" t="s">
         <v>21</v>
       </c>
@@ -1738,10 +1738,10 @@
       <c r="C5" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="47" t="s">
+      <c r="D5" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="48"/>
+      <c r="E5" s="49"/>
       <c r="H5" s="25" t="s">
         <v>22</v>
       </c>
@@ -1757,19 +1757,19 @@
       <c r="C6" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="43" t="s">
+      <c r="D6" s="44" t="s">
         <v>72</v>
       </c>
-      <c r="E6" s="43"/>
+      <c r="E6" s="44"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C7" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="43" t="s">
+      <c r="D7" s="44" t="s">
         <v>70</v>
       </c>
-      <c r="E7" s="43"/>
+      <c r="E7" s="44"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" s="28" t="s">
@@ -2027,19 +2027,19 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="38" t="s">
+      <c r="H1" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="39" t="s">
+      <c r="B2" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
       <c r="H2" s="3"/>
       <c r="I2" s="16" t="s">
         <v>30</v>
@@ -2063,10 +2063,10 @@
       <c r="C4" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="49" t="s">
+      <c r="D4" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="49"/>
+      <c r="E4" s="50"/>
       <c r="H4" s="14" t="s">
         <v>21</v>
       </c>
@@ -2081,10 +2081,10 @@
       <c r="C5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="50" t="s">
+      <c r="D5" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="51"/>
+      <c r="E5" s="52"/>
       <c r="H5" s="14" t="s">
         <v>22</v>
       </c>
@@ -2100,19 +2100,19 @@
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="41" t="s">
+      <c r="D6" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="41"/>
+      <c r="E6" s="42"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="42">
+      <c r="D7" s="43">
         <v>46097</v>
       </c>
-      <c r="E7" s="41"/>
+      <c r="E7" s="42"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" s="10" t="s">
@@ -2309,7 +2309,9 @@
         <v>8</v>
       </c>
       <c r="D28" s="12"/>
-      <c r="E28" s="1"/>
+      <c r="E28" s="1">
+        <v>1.5</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -2348,19 +2350,19 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="38" t="s">
+      <c r="H1" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="39" t="s">
+      <c r="B2" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
       <c r="H2" s="3"/>
       <c r="I2" s="16" t="s">
         <v>30</v>
@@ -2384,10 +2386,10 @@
       <c r="C4" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="40" t="s">
+      <c r="D4" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="40"/>
+      <c r="E4" s="41"/>
       <c r="H4" s="14" t="s">
         <v>21</v>
       </c>
@@ -2402,10 +2404,10 @@
       <c r="C5" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="52" t="s">
+      <c r="D5" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="53"/>
+      <c r="E5" s="54"/>
       <c r="H5" s="14" t="s">
         <v>22</v>
       </c>
@@ -2421,19 +2423,19 @@
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="41" t="s">
+      <c r="D6" s="42" t="s">
         <v>73</v>
       </c>
-      <c r="E6" s="41"/>
+      <c r="E6" s="42"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="42">
+      <c r="D7" s="43">
         <v>46097</v>
       </c>
-      <c r="E7" s="41"/>
+      <c r="E7" s="42"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" s="10" t="s">
@@ -2463,7 +2465,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B11" s="3">
         <f>B10+1</f>
         <v>2</v>
@@ -2732,19 +2734,19 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="38" t="s">
+      <c r="H1" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="39" t="s">
+      <c r="B2" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
       <c r="H2" s="3"/>
       <c r="I2" s="16" t="s">
         <v>30</v>
@@ -2768,10 +2770,10 @@
       <c r="C4" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="40" t="s">
+      <c r="D4" s="41" t="s">
         <v>96</v>
       </c>
-      <c r="E4" s="40"/>
+      <c r="E4" s="41"/>
       <c r="H4" s="14" t="s">
         <v>21</v>
       </c>
@@ -2786,10 +2788,10 @@
       <c r="C5" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="41" t="s">
+      <c r="D5" s="42" t="s">
         <v>73</v>
       </c>
-      <c r="E5" s="41"/>
+      <c r="E5" s="42"/>
       <c r="H5" s="14" t="s">
         <v>22</v>
       </c>
@@ -2805,10 +2807,10 @@
       <c r="C6" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="42">
+      <c r="D6" s="43">
         <v>46097</v>
       </c>
-      <c r="E6" s="41"/>
+      <c r="E6" s="42"/>
       <c r="F6" s="17"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
@@ -3066,11 +3068,11 @@
       <c r="F30" s="2"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="C32" s="36" t="s">
+      <c r="C32" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="D32" s="37"/>
-      <c r="E32" s="37"/>
+      <c r="D32" s="38"/>
+      <c r="E32" s="38"/>
       <c r="F32" s="15">
         <v>1</v>
       </c>
@@ -3079,7 +3081,7 @@
       <c r="F35" s="18"/>
     </row>
     <row r="36" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C36" s="54" t="s">
+      <c r="C36" s="36" t="s">
         <v>109</v>
       </c>
     </row>
